--- a/unit3_databaseDesign/datasets/unit3e_Music.xlsx
+++ b/unit3_databaseDesign/datasets/unit3e_Music.xlsx
@@ -488,7 +488,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. Open it in Google Sheets (File → Import → Upload). Share it with your partner so you both can edit.</t>
+          <t>1. Open it in Microsoft Excel. Save it in your repo as unit3e_Music_lastname.xlsx. Work on one copy with your partner.</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Copy the columns you need from the 1NF tab, then use Data → Data cleanup → Remove duplicates.</t>
+          <t xml:space="preserve">   Copy the columns you need from the 1NF tab, then use Data → Remove Duplicates (check 'My data has headers').</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>7. When you finish, answer the questions in unit3e_Music_lastname.md and paste your table designs there.</t>
+          <t>7. When you finish, answer the questions in unit3e_Music_lastname.md and paste your table designs there. Commit this Excel file too.</t>
         </is>
       </c>
     </row>
